--- a/artfynd/A 3472-2023 artfynd.xlsx
+++ b/artfynd/A 3472-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3472-2023 artfynd.xlsx
+++ b/artfynd/A 3472-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105316092</v>
+        <v>105314251</v>
       </c>
       <c r="B2" t="n">
-        <v>4808</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101675</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694917.7623629319</v>
+        <v>694816</v>
       </c>
       <c r="R2" t="n">
-        <v>6623209.02155358</v>
+        <v>6623078</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,21 +743,11 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På avkapad stubbe av gran.</t>
+        </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -792,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105310075</v>
+        <v>105314249</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Upl</t>
+          <t>Huvan, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694973.1061969951</v>
+        <v>694820</v>
       </c>
       <c r="R3" t="n">
-        <v>6622954.539169639</v>
+        <v>6622938</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,21 +850,11 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,11 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -914,37 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105314251</v>
+        <v>105314250</v>
       </c>
       <c r="B4" t="n">
-        <v>90052</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694816.2261854571</v>
+        <v>694820</v>
       </c>
       <c r="R4" t="n">
-        <v>6623077.811537536</v>
+        <v>6622987</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,21 +952,11 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,11 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>På avkapad stubbe av gran.</t>
-        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1036,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105314254</v>
+        <v>105314252</v>
       </c>
       <c r="B5" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694914.6262219052</v>
+        <v>694895</v>
       </c>
       <c r="R5" t="n">
-        <v>6623210.880156469</v>
+        <v>6623262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,19 +1054,9 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,15 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105310521</v>
+        <v>112519828</v>
       </c>
       <c r="B6" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,37 +1099,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästhagen, Upl</t>
+          <t>Hästhagen, Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695064.8594866947</v>
+        <v>694882</v>
       </c>
       <c r="R6" t="n">
-        <v>6622962.876795201</v>
+        <v>6623059</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,22 +1154,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,41 +1180,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>På större block.</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105310520</v>
+        <v>105310519</v>
       </c>
       <c r="B7" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,12 +1216,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695056.7770425754</v>
+        <v>695063</v>
       </c>
       <c r="R7" t="n">
-        <v>6622962.454057364</v>
+        <v>6622973</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,21 +1264,11 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1374,7 +1280,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På gammal asp.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1397,37 +1303,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105314250</v>
+        <v>105310520</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1437,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694820.4891685704</v>
+        <v>695057</v>
       </c>
       <c r="R8" t="n">
-        <v>6622986.510898281</v>
+        <v>6622962</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,21 +1371,11 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1493,6 +1384,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>På gammal asp.</t>
+        </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -1514,37 +1410,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105314253</v>
+        <v>105310521</v>
       </c>
       <c r="B9" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1554,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694887.6002102672</v>
+        <v>695065</v>
       </c>
       <c r="R9" t="n">
-        <v>6623233.737856566</v>
+        <v>6622963</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,21 +1478,11 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1610,6 +1491,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>På större block.</t>
+        </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -1631,15 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105310077</v>
+        <v>105314254</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,34 +1528,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>4660</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Huvan, Upl</t>
+          <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694831.8784440504</v>
+        <v>694915</v>
       </c>
       <c r="R10" t="n">
-        <v>6622952.720842401</v>
+        <v>6623211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,19 +1585,9 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,15 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105310519</v>
+        <v>112517026</v>
       </c>
       <c r="B11" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,37 +1630,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2667</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästhagen, Upl</t>
+          <t>Hästhagen, Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>695062.8165048382</v>
+        <v>695238</v>
       </c>
       <c r="R11" t="n">
-        <v>6622972.88326818</v>
+        <v>6622997</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,22 +1685,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,63 +1711,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105310078</v>
+        <v>105314253</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1910,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694800.9419538418</v>
+        <v>694888</v>
       </c>
       <c r="R12" t="n">
-        <v>6623137.690332536</v>
+        <v>6623234</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1943,19 +1795,9 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,15 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105314252</v>
+        <v>112517708</v>
       </c>
       <c r="B13" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,37 +1840,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>6268</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hästhagen, Upl</t>
+          <t>Hästhagen, Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694895.2164523902</v>
+        <v>694871</v>
       </c>
       <c r="R13" t="n">
-        <v>6623262.450962785</v>
+        <v>6623217</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2057,22 +1895,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,36 +1921,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105310076</v>
+        <v>105316092</v>
       </c>
       <c r="B14" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,34 +1948,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>101675</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Huvan, Upl</t>
+          <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694910.0629927341</v>
+        <v>694918</v>
       </c>
       <c r="R14" t="n">
-        <v>6622939.61349347</v>
+        <v>6623209</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2177,19 +2005,9 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,15 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105314249</v>
+        <v>112517102</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,37 +2050,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Huvan, Upl</t>
+          <t>Hästhagen, Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694819.987213979</v>
+        <v>695073</v>
       </c>
       <c r="R15" t="n">
-        <v>6622937.941009366</v>
+        <v>6623049</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2291,22 +2105,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2317,36 +2131,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112517708</v>
+        <v>105310075</v>
       </c>
       <c r="B16" t="n">
-        <v>88275</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,38 +2158,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6268</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästhagen (Hästhagen), Upl</t>
+          <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>694872</v>
+        <v>694973</v>
       </c>
       <c r="R16" t="n">
-        <v>6623216</v>
+        <v>6622955</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2409,22 +2212,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,31 +2228,36 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112517026</v>
+        <v>105310076</v>
       </c>
       <c r="B17" t="n">
-        <v>90588</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,38 +2265,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästhagen (Hästhagen), Upl</t>
+          <t>Huvan, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695238</v>
+        <v>694910</v>
       </c>
       <c r="R17" t="n">
-        <v>6622997</v>
+        <v>6622940</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2522,22 +2319,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,31 +2335,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112517102</v>
+        <v>105310077</v>
       </c>
       <c r="B18" t="n">
-        <v>100035</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,38 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästhagen (Hästhagen), Upl</t>
+          <t>Huvan, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695073</v>
+        <v>694832</v>
       </c>
       <c r="R18" t="n">
-        <v>6623049</v>
+        <v>6622953</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2635,22 +2421,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,31 +2437,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112519828</v>
+        <v>105310078</v>
       </c>
       <c r="B19" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,38 +2469,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästhagen (Hästhagen), Upl</t>
+          <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>694882</v>
+        <v>694801</v>
       </c>
       <c r="R19" t="n">
-        <v>6623059</v>
+        <v>6623138</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2748,22 +2523,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2774,16 +2539,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 3472-2023 artfynd.xlsx
+++ b/artfynd/A 3472-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314251</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314249</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314250</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314252</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112519828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310519</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310520</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310521</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314254</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517026</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,6 +1881,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314253</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517708</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2036,6 +2101,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316092</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517102</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310075</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2353,6 +2433,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310076</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2455,6 +2540,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310077</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2557,8 +2647,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310078</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>